--- a/excel/intake_template.xlsx
+++ b/excel/intake_template.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
@@ -944,15 +944,20 @@
       </c>
       <c r="M1" s="18" t="inlineStr">
         <is>
+          <t>ct_class</t>
+        </is>
+      </c>
+      <c r="N1" s="18" t="inlineStr">
+        <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1009,17 +1014,22 @@
       </c>
       <c r="K2" s="19" t="n"/>
       <c r="L2" s="19" t="n"/>
-      <c r="M2" s="19" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5P20</t>
+        </is>
+      </c>
+      <c r="N2" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="N2" s="19" t="inlineStr">
+      <c r="O2" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="O2" s="19" t="inlineStr">
+      <c r="P2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1044,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1217,53 +1227,61 @@
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="7" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
       <c r="B20" s="7" t="n"/>
     </row>
     <row r="21">
@@ -1285,6 +1303,10 @@
     <row r="25">
       <c r="A25" s="4" t="n"/>
       <c r="B25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_template.xlsx
+++ b/excel/intake_template.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -934,30 +934,35 @@
       </c>
       <c r="K1" s="18" t="inlineStr">
         <is>
+          <t>ct_differential</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1012,24 +1017,24 @@
           <t>1200:5A (3)</t>
         </is>
       </c>
-      <c r="K2" s="19" t="n"/>
       <c r="L2" s="19" t="n"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="19" t="n"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>5P20</t>
         </is>
       </c>
-      <c r="N2" s="19" t="inlineStr">
+      <c r="O2" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="O2" s="19" t="inlineStr">
+      <c r="P2" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="P2" s="19" t="inlineStr">
+      <c r="Q2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1054,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1203,89 +1208,97 @@
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="7" t="n"/>
-    </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
       <c r="B21" s="7" t="n"/>
     </row>
     <row r="22">
@@ -1307,6 +1320,10 @@
     <row r="26">
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_template.xlsx
+++ b/excel/intake_template.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -929,40 +929,45 @@
       </c>
       <c r="J1" s="18" t="inlineStr">
         <is>
+          <t>bus_differential</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1012,29 +1017,30 @@
           <t>SEL-751</t>
         </is>
       </c>
-      <c r="J2" s="19" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr"/>
+      <c r="K2" s="19" t="inlineStr">
         <is>
           <t>1200:5A (3)</t>
         </is>
       </c>
-      <c r="L2" s="19" t="n"/>
       <c r="M2" s="19" t="n"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="19" t="n"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>5P20</t>
         </is>
       </c>
-      <c r="O2" s="19" t="inlineStr">
+      <c r="P2" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="P2" s="19" t="inlineStr">
+      <c r="Q2" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="Q2" s="19" t="inlineStr">
+      <c r="R2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1059,7 +1065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1196,113 +1202,121 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="7" t="n"/>
-    </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
       <c r="B22" s="7" t="n"/>
     </row>
     <row r="23">
@@ -1324,6 +1338,10 @@
     <row r="27">
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_template.xlsx
+++ b/excel/intake_template.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -929,45 +929,50 @@
       </c>
       <c r="J1" s="18" t="inlineStr">
         <is>
+          <t>relay_fuse</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
           <t>bus_differential</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1018,29 +1023,30 @@
         </is>
       </c>
       <c r="J2" s="19" t="inlineStr"/>
-      <c r="K2" s="19" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr"/>
+      <c r="L2" s="19" t="inlineStr">
         <is>
           <t>1200:5A (3)</t>
         </is>
       </c>
-      <c r="M2" s="19" t="n"/>
       <c r="N2" s="19" t="n"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="19" t="n"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5P20</t>
         </is>
       </c>
-      <c r="P2" s="19" t="inlineStr">
+      <c r="Q2" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="Q2" s="19" t="inlineStr">
+      <c r="R2" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="R2" s="19" t="inlineStr">
+      <c r="S2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1065,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1202,125 +1208,133 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>bus_differential</t>
+          <t>relay_fuse</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
+          <t>Optional. Fuse on this relay's supply where it drops off the reference run, e.g. 6A. Leave blank to take the house default.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="7" t="n"/>
-    </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
       <c r="B23" s="7" t="n"/>
     </row>
     <row r="24">
@@ -1342,6 +1356,10 @@
     <row r="28">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_template.xlsx
+++ b/excel/intake_template.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -909,70 +909,75 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
           <t>voltage</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>amp_rating</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>ka_rating</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>relay</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>relay_fuse</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>bus_differential</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="S1" s="18" t="inlineStr">
+      <c r="T1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1002,51 +1007,52 @@
           <t>MAIN BREAKER</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr"/>
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>15kV</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>1200A</t>
         </is>
       </c>
-      <c r="H2" s="19" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>25kA</t>
         </is>
       </c>
-      <c r="I2" s="19" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>SEL-751</t>
         </is>
       </c>
-      <c r="J2" s="19" t="inlineStr"/>
       <c r="K2" s="19" t="inlineStr"/>
-      <c r="L2" s="19" t="inlineStr">
+      <c r="L2" s="19" t="inlineStr"/>
+      <c r="M2" s="19" t="inlineStr">
         <is>
           <t>1200:5A (3)</t>
         </is>
       </c>
-      <c r="N2" s="19" t="n"/>
       <c r="O2" s="19" t="n"/>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="19" t="n"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>5P20</t>
         </is>
       </c>
-      <c r="Q2" s="19" t="inlineStr">
+      <c r="R2" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="R2" s="19" t="inlineStr">
+      <c r="S2" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="S2" s="19" t="inlineStr">
+      <c r="T2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1071,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1160,185 +1166,193 @@
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>voltage</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Breaker rated maximum voltage, e.g. 15kV.</t>
+          <t>Fill on the bus tie, with its normal position, e.g. N.C. The breaker is then drawn lying IN the bus instead of hanging off it, and the bus breaks there -- which is what makes the lineup two buses instead of one.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>amp_rating</t>
+          <t>voltage</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Breaker continuous current. BLANK MEANS NO BREAKER -- that is how a deck holds only a bus PT.</t>
+          <t>Breaker rated maximum voltage, e.g. 15kV.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>ka_rating</t>
+          <t>amp_rating</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Breaker interrupting rating.</t>
+          <t>Breaker continuous current. BLANK MEANS NO BREAKER -- that is how a deck holds only a bus PT.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>relay</t>
+          <t>ka_rating</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Protection relay model. Drawn as a labelled box beside the breaker.</t>
+          <t>Breaker interrupting rating.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>relay_fuse</t>
+          <t>relay</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Optional. Fuse on this relay's supply where it drops off the reference run, e.g. 6A. Leave blank to take the house default.</t>
+          <t>Protection relay model. Drawn as a labelled box beside the breaker.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>bus_differential</t>
+          <t>relay_fuse</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
+          <t>Optional. Fuse on this relay's supply where it drops off the reference run, e.g. 6A. Leave blank to take the house default.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="7" t="n"/>
-    </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
       <c r="B24" s="7" t="n"/>
     </row>
     <row r="25">
@@ -1360,6 +1374,10 @@
     <row r="29">
       <c r="A29" s="4" t="n"/>
       <c r="B29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_template.xlsx
+++ b/excel/intake_template.xlsx
@@ -861,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -939,45 +939,50 @@
       </c>
       <c r="L1" s="18" t="inlineStr">
         <is>
+          <t>merging_unit</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
           <t>bus_differential</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="S1" s="18" t="inlineStr">
+      <c r="T1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="T1" s="18" t="inlineStr">
+      <c r="U1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1029,30 +1034,31 @@
         </is>
       </c>
       <c r="K2" s="19" t="inlineStr"/>
-      <c r="L2" s="19" t="inlineStr"/>
-      <c r="M2" s="19" t="inlineStr">
+      <c r="L2" s="19" t="n"/>
+      <c r="M2" s="19" t="inlineStr"/>
+      <c r="N2" s="19" t="inlineStr">
         <is>
           <t>1200:5A (3)</t>
         </is>
       </c>
-      <c r="O2" s="19" t="n"/>
       <c r="P2" s="19" t="n"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="19" t="n"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>5P20</t>
         </is>
       </c>
-      <c r="R2" s="19" t="inlineStr">
+      <c r="S2" s="19" t="inlineStr">
         <is>
           <t>14,400:120V</t>
         </is>
       </c>
-      <c r="S2" s="19" t="inlineStr">
+      <c r="T2" s="19" t="inlineStr">
         <is>
           <t>CLF 0.5E</t>
         </is>
       </c>
-      <c r="T2" s="19" t="inlineStr">
+      <c r="U2" s="19" t="inlineStr">
         <is>
           <t>UTILITY SUPPLY 13.8kV, 3PH, 60HZ</t>
         </is>
@@ -1077,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1238,125 +1244,133 @@
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>bus_differential</t>
+          <t>merging_unit</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
+          <t>Merging unit model, e.g. 6MU85. Drawn as a second box beside the relay, fed by its own CT and by one bus's voltage reference. Tie cubicles only.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="7" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n"/>
       <c r="B25" s="7" t="n"/>
     </row>
     <row r="26">
@@ -1378,6 +1392,10 @@
     <row r="30">
       <c r="A30" s="4" t="n"/>
       <c r="B30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
